--- a/enrollment/046_new_hire_onboarding_form--enrollment.xlsx
+++ b/enrollment/046_new_hire_onboarding_form--enrollment.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'full-time',_'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Full-time', 'value': 'full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'part-time',_'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Part-time', 'value': 'part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'contract',_'value':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Contract', 'value': 'contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'spouse',_'value':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Spouse', 'value': 'spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'partner',_'value':_'partner'}</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Partner', 'value': 'partner'}</t>
+          <t>Partner</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'friend',_'value':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Friend', 'value': 'friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'family',_'value':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Family', 'value': 'family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'spouse',_'value':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Spouse', 'value': 'spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'partner',_'value':_'partner'}</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Partner', 'value': 'partner'}</t>
+          <t>Partner</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'friend',_'value':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Friend', 'value': 'friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'family',_'value':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Family', 'value': 'family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
